--- a/xlsx/carteira_mensal/Mai_2026.xlsx
+++ b/xlsx/carteira_mensal/Mai_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="116">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -231,7 +231,7 @@
     <t>Néllida Dellai</t>
   </si>
   <si>
-    <t>Indicação de Amigos</t>
+    <t>Indicação de outros clientes</t>
   </si>
   <si>
     <t>11/05/26</t>
@@ -307,9 +307,6 @@
   </si>
   <si>
     <t>Jose Costa de Araujo</t>
-  </si>
-  <si>
-    <t>Indicação de outros clientes</t>
   </si>
   <si>
     <t>28/05/26</t>
@@ -1627,13 +1624,13 @@
         <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C51" t="n">
         <v>820.0</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51" t="s">
         <v>49</v>
@@ -1666,12 +1663,12 @@
         <v>82001.0</v>
       </c>
       <c r="O51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
         <v>88</v>
@@ -1680,7 +1677,7 @@
         <v>818.0</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
@@ -1692,7 +1689,7 @@
         <v>50</v>
       </c>
       <c r="H52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I52" t="n">
         <v>300.0</v>
@@ -1713,39 +1710,39 @@
         <v>81801.0</v>
       </c>
       <c r="O52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="59">
@@ -1753,39 +1750,39 @@
         <v>17</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Mai_2026.xlsx
+++ b/xlsx/carteira_mensal/Mai_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="119">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/05/2026 até 31/05/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,6 +153,24 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Claudia Cintra de Marchi</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>09/04/26</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>Orçamento 2</t>
+  </si>
+  <si>
+    <t>13/05/26</t>
+  </si>
+  <si>
     <t>Romulo Gimenes Ralha</t>
   </si>
   <si>
@@ -186,9 +204,6 @@
     <t>joao marcelo correa cunha</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
@@ -210,9 +225,6 @@
     <t>08/05/26</t>
   </si>
   <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
     <t>WILLIAM WU</t>
   </si>
   <si>
@@ -243,9 +255,6 @@
     <t>Douglas monteiro da silva godinho</t>
   </si>
   <si>
-    <t>13/05/26</t>
-  </si>
-  <si>
     <t>Luiz Felipe Reboredo Nunes</t>
   </si>
   <si>
@@ -318,7 +327,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -327,40 +336,40 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.90</t>
+    <t>1.91</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>633.792,32</t>
-  </si>
-  <si>
-    <t>452.462,30</t>
+    <t>641.567,28</t>
+  </si>
+  <si>
+    <t>459.062,30</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>412.438,49</t>
+    <t>418.794,30</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>394.663,55</t>
+    <t>401.019,36</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>40.023,81</t>
+    <t>40.268,00</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>28.145,22</t>
+    <t>28.619,31</t>
   </si>
 </sst>
 </file>
@@ -429,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O63"/>
+  <dimension ref="A2:O64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.16796875" customWidth="true" bestFit="true"/>
@@ -557,15 +566,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +582,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +590,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -687,7 +696,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>766.0</v>
+        <v>732.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -696,172 +705,172 @@
         <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" t="s">
         <v>50</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>15895.74</v>
+        <v>6600.0</v>
       </c>
       <c r="J31" t="n">
-        <v>3738.33</v>
+        <v>244.19</v>
       </c>
       <c r="K31" t="n">
-        <v>12157.41</v>
+        <v>6355.81</v>
       </c>
       <c r="L31" t="n">
-        <v>11866.7</v>
+        <v>6355.81</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="N31" t="n">
-        <v>76601.0</v>
+        <v>73202.0</v>
       </c>
       <c r="O31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>772.0</v>
+        <v>766.0</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
         <v>1.0</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I32" t="n">
-        <v>300.0</v>
+        <v>15895.74</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0</v>
+        <v>3738.33</v>
       </c>
       <c r="K32" t="n">
-        <v>300.0</v>
+        <v>12157.41</v>
       </c>
       <c r="L32" t="n">
-        <v>300.0</v>
+        <v>11866.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.27</v>
+        <v>1.9</v>
       </c>
       <c r="N32" t="n">
-        <v>77201.0</v>
+        <v>76601.0</v>
       </c>
       <c r="O32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
-        <v>771.0</v>
+        <v>772.0</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I33" t="n">
-        <v>2035.0</v>
+        <v>300.0</v>
       </c>
       <c r="J33" t="n">
-        <v>123.41</v>
+        <v>0.0</v>
       </c>
       <c r="K33" t="n">
-        <v>1911.59</v>
+        <v>300.0</v>
       </c>
       <c r="L33" t="n">
-        <v>1911.59</v>
+        <v>300.0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>77101.0</v>
+        <v>77201.0</v>
       </c>
       <c r="O33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
-        <v>769.0</v>
+        <v>771.0</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H34" t="s">
         <v>59</v>
       </c>
       <c r="I34" t="n">
-        <v>56000.0</v>
+        <v>2035.0</v>
       </c>
       <c r="J34" t="n">
-        <v>3423.25</v>
+        <v>123.41</v>
       </c>
       <c r="K34" t="n">
-        <v>52576.75</v>
+        <v>1911.59</v>
       </c>
       <c r="L34" t="n">
-        <v>52576.75</v>
+        <v>1911.59</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N34" t="n">
-        <v>76901.0</v>
+        <v>77101.0</v>
       </c>
       <c r="O34" t="s">
         <v>59</v>
@@ -869,237 +878,237 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C35" t="n">
-        <v>777.0</v>
+        <v>769.0</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G35" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I35" t="n">
-        <v>196.0</v>
+        <v>56000.0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0</v>
+        <v>3423.25</v>
       </c>
       <c r="K35" t="n">
-        <v>196.0</v>
+        <v>52576.75</v>
       </c>
       <c r="L35" t="n">
-        <v>196.0</v>
+        <v>52576.75</v>
       </c>
       <c r="M35" t="n">
-        <v>4.0</v>
+        <v>1.9</v>
       </c>
       <c r="N35" t="n">
-        <v>77701.0</v>
+        <v>76901.0</v>
       </c>
       <c r="O35" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C36" t="n">
-        <v>781.0</v>
+        <v>777.0</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I36" t="n">
-        <v>850.0</v>
+        <v>196.0</v>
       </c>
       <c r="J36" t="n">
-        <v>73.52</v>
+        <v>0.0</v>
       </c>
       <c r="K36" t="n">
-        <v>776.48</v>
+        <v>196.0</v>
       </c>
       <c r="L36" t="n">
-        <v>776.48</v>
+        <v>196.0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.11</v>
+        <v>4.0</v>
       </c>
       <c r="N36" t="n">
-        <v>78101.0</v>
+        <v>77701.0</v>
       </c>
       <c r="O36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C37" t="n">
-        <v>780.0</v>
+        <v>781.0</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G37" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H37" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I37" t="n">
-        <v>978.7</v>
+        <v>850.0</v>
       </c>
       <c r="J37" t="n">
-        <v>70.56</v>
+        <v>73.52</v>
       </c>
       <c r="K37" t="n">
-        <v>908.14</v>
+        <v>776.48</v>
       </c>
       <c r="L37" t="n">
-        <v>908.14</v>
+        <v>776.48</v>
       </c>
       <c r="M37" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="N37" t="n">
-        <v>78001.0</v>
+        <v>78101.0</v>
       </c>
       <c r="O37" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C38" t="n">
-        <v>783.0</v>
+        <v>780.0</v>
       </c>
       <c r="D38" t="s">
         <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
       </c>
       <c r="G38" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I38" t="n">
-        <v>2450.75</v>
+        <v>978.7</v>
       </c>
       <c r="J38" t="n">
-        <v>229.66</v>
+        <v>70.56</v>
       </c>
       <c r="K38" t="n">
-        <v>2221.09</v>
+        <v>908.14</v>
       </c>
       <c r="L38" t="n">
-        <v>2221.09</v>
+        <v>908.14</v>
       </c>
       <c r="M38" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="N38" t="n">
-        <v>78301.0</v>
+        <v>78001.0</v>
       </c>
       <c r="O38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C39" t="n">
-        <v>784.0</v>
+        <v>783.0</v>
       </c>
       <c r="D39" t="s">
         <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
       </c>
       <c r="G39" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I39" t="n">
-        <v>8740.0</v>
+        <v>2450.75</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0</v>
+        <v>229.66</v>
       </c>
       <c r="K39" t="n">
-        <v>8740.0</v>
+        <v>2221.09</v>
       </c>
       <c r="L39" t="n">
-        <v>8740.0</v>
+        <v>2221.09</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>2.17</v>
       </c>
       <c r="N39" t="n">
-        <v>78401.0</v>
+        <v>78301.0</v>
       </c>
       <c r="O39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
@@ -1107,140 +1116,140 @@
         <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C40" t="n">
-        <v>789.0</v>
+        <v>784.0</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
       </c>
       <c r="G40" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I40" t="n">
-        <v>1500.0</v>
+        <v>8740.0</v>
       </c>
       <c r="J40" t="n">
-        <v>129.74</v>
+        <v>0.0</v>
       </c>
       <c r="K40" t="n">
-        <v>1370.26</v>
+        <v>8740.0</v>
       </c>
       <c r="L40" t="n">
-        <v>1370.26</v>
+        <v>8740.0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.11</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>78901.0</v>
+        <v>78401.0</v>
       </c>
       <c r="O40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>791.0</v>
+        <v>789.0</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H41" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="I41" t="n">
-        <v>1705.06</v>
+        <v>1500.0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0</v>
+        <v>129.74</v>
       </c>
       <c r="K41" t="n">
-        <v>1705.06</v>
+        <v>1370.26</v>
       </c>
       <c r="L41" t="n">
-        <v>1705.06</v>
+        <v>1370.26</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="N41" t="n">
-        <v>79101.0</v>
+        <v>78901.0</v>
       </c>
       <c r="O41" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C42" t="n">
-        <v>792.0</v>
+        <v>791.0</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F42" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H42" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I42" t="n">
-        <v>50000.0</v>
+        <v>1705.06</v>
       </c>
       <c r="J42" t="n">
-        <v>3175.47</v>
+        <v>0.0</v>
       </c>
       <c r="K42" t="n">
-        <v>46824.53</v>
+        <v>1705.06</v>
       </c>
       <c r="L42" t="n">
-        <v>45692.38</v>
+        <v>1705.06</v>
       </c>
       <c r="M42" t="n">
-        <v>2.11</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>79201.0</v>
+        <v>79101.0</v>
       </c>
       <c r="O42" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43">
@@ -1248,184 +1257,184 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C43" t="n">
-        <v>797.0</v>
+        <v>792.0</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E43" t="s">
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G43" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I43" t="n">
-        <v>27200.0</v>
+        <v>50000.0</v>
       </c>
       <c r="J43" t="n">
-        <v>3454.92</v>
+        <v>3175.47</v>
       </c>
       <c r="K43" t="n">
-        <v>23745.08</v>
+        <v>46824.53</v>
       </c>
       <c r="L43" t="n">
-        <v>23184.01</v>
+        <v>45692.38</v>
       </c>
       <c r="M43" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="N43" t="n">
-        <v>79701.0</v>
+        <v>79201.0</v>
       </c>
       <c r="O43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="n">
+        <v>797.0</v>
+      </c>
+      <c r="D44" t="s">
         <v>83</v>
       </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="n">
-        <v>796.0</v>
-      </c>
-      <c r="D44" t="s">
-        <v>80</v>
-      </c>
       <c r="E44" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
       </c>
       <c r="G44" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I44" t="n">
-        <v>40432.06</v>
+        <v>27200.0</v>
       </c>
       <c r="J44" t="n">
-        <v>11941.12</v>
+        <v>3454.92</v>
       </c>
       <c r="K44" t="n">
-        <v>28490.94</v>
+        <v>23745.08</v>
       </c>
       <c r="L44" t="n">
-        <v>28490.94</v>
+        <v>23184.01</v>
       </c>
       <c r="M44" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="N44" t="n">
-        <v>79601.0</v>
+        <v>79701.0</v>
       </c>
       <c r="O44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C45" t="n">
-        <v>802.0</v>
+        <v>796.0</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F45" t="n">
         <v>1.0</v>
       </c>
       <c r="G45" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I45" t="n">
-        <v>300.0</v>
+        <v>40432.06</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0</v>
+        <v>11941.12</v>
       </c>
       <c r="K45" t="n">
-        <v>300.0</v>
+        <v>28490.94</v>
       </c>
       <c r="L45" t="n">
-        <v>300.0</v>
+        <v>28490.94</v>
       </c>
       <c r="M45" t="n">
-        <v>3.0</v>
+        <v>2.1</v>
       </c>
       <c r="N45" t="n">
-        <v>80201.0</v>
+        <v>79601.0</v>
       </c>
       <c r="O45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C46" t="n">
-        <v>808.0</v>
+        <v>802.0</v>
       </c>
       <c r="D46" t="s">
         <v>89</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F46" t="n">
         <v>1.0</v>
       </c>
       <c r="G46" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H46" t="s">
         <v>89</v>
       </c>
       <c r="I46" t="n">
-        <v>171000.0</v>
+        <v>300.0</v>
       </c>
       <c r="J46" t="n">
-        <v>8296.22</v>
+        <v>0.0</v>
       </c>
       <c r="K46" t="n">
-        <v>162703.78</v>
+        <v>300.0</v>
       </c>
       <c r="L46" t="n">
-        <v>147859.41</v>
+        <v>300.0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.9</v>
+        <v>3.0</v>
       </c>
       <c r="N46" t="n">
-        <v>80801.0</v>
+        <v>80201.0</v>
       </c>
       <c r="O46" t="s">
         <v>89</v>
@@ -1439,43 +1448,43 @@
         <v>91</v>
       </c>
       <c r="C47" t="n">
-        <v>810.0</v>
+        <v>808.0</v>
       </c>
       <c r="D47" t="s">
         <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F47" t="n">
         <v>1.0</v>
       </c>
       <c r="G47" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H47" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I47" t="n">
-        <v>44999.99</v>
+        <v>171000.0</v>
       </c>
       <c r="J47" t="n">
-        <v>4261.29</v>
+        <v>8296.22</v>
       </c>
       <c r="K47" t="n">
-        <v>40738.7</v>
+        <v>162703.78</v>
       </c>
       <c r="L47" t="n">
-        <v>39792.06</v>
+        <v>147859.41</v>
       </c>
       <c r="M47" t="n">
         <v>1.9</v>
       </c>
       <c r="N47" t="n">
-        <v>81001.0</v>
+        <v>80801.0</v>
       </c>
       <c r="O47" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
@@ -1483,255 +1492,294 @@
         <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C48" t="n">
-        <v>809.0</v>
+        <v>810.0</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F48" t="n">
         <v>1.0</v>
       </c>
       <c r="G48" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H48" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I48" t="n">
-        <v>20800.0</v>
+        <v>44999.99</v>
       </c>
       <c r="J48" t="n">
-        <v>763.21</v>
+        <v>4261.29</v>
       </c>
       <c r="K48" t="n">
-        <v>20036.79</v>
+        <v>40738.7</v>
       </c>
       <c r="L48" t="n">
-        <v>20036.79</v>
+        <v>39792.06</v>
       </c>
       <c r="M48" t="n">
         <v>1.9</v>
       </c>
       <c r="N48" t="n">
-        <v>80901.0</v>
+        <v>81001.0</v>
       </c>
       <c r="O48" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C49" t="n">
-        <v>815.0</v>
+        <v>809.0</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E49" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>56</v>
+      </c>
+      <c r="H49" t="s">
         <v>95</v>
       </c>
-      <c r="F49" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>50</v>
-      </c>
-      <c r="H49" t="s">
-        <v>84</v>
-      </c>
       <c r="I49" t="n">
-        <v>3000.0</v>
+        <v>20800.0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0</v>
+        <v>763.21</v>
       </c>
       <c r="K49" t="n">
-        <v>3000.0</v>
+        <v>20036.79</v>
       </c>
       <c r="L49" t="n">
-        <v>3000.0</v>
+        <v>20036.79</v>
       </c>
       <c r="M49" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="N49" t="n">
-        <v>81501.0</v>
+        <v>80901.0</v>
       </c>
       <c r="O49" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>811.0</v>
+        <v>815.0</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G50" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I50" t="n">
-        <v>2056.0</v>
+        <v>3000.0</v>
       </c>
       <c r="J50" t="n">
-        <v>194.09</v>
+        <v>0.0</v>
       </c>
       <c r="K50" t="n">
-        <v>1861.91</v>
+        <v>3000.0</v>
       </c>
       <c r="L50" t="n">
-        <v>1861.91</v>
+        <v>3000.0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.01</v>
+        <v>2.02</v>
       </c>
       <c r="N50" t="n">
-        <v>81101.0</v>
+        <v>81501.0</v>
       </c>
       <c r="O50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>820.0</v>
+        <v>811.0</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F51" t="n">
         <v>1.0</v>
       </c>
       <c r="G51" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H51" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I51" t="n">
-        <v>1723.0</v>
+        <v>2056.0</v>
       </c>
       <c r="J51" t="n">
-        <v>149.02</v>
+        <v>194.09</v>
       </c>
       <c r="K51" t="n">
-        <v>1573.98</v>
+        <v>1861.91</v>
       </c>
       <c r="L51" t="n">
-        <v>1573.98</v>
+        <v>1861.91</v>
       </c>
       <c r="M51" t="n">
-        <v>1.25</v>
+        <v>3.01</v>
       </c>
       <c r="N51" t="n">
-        <v>82001.0</v>
+        <v>81101.0</v>
       </c>
       <c r="O51" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C52" t="n">
+        <v>820.0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>56</v>
+      </c>
+      <c r="H52" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1723.0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>149.02</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1573.98</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1573.98</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>82001.0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" t="n">
         <v>818.0</v>
       </c>
-      <c r="D52" t="s">
-        <v>98</v>
-      </c>
-      <c r="E52" t="s">
-        <v>49</v>
-      </c>
-      <c r="F52" t="n">
+      <c r="D53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" t="n">
         <v>3.0</v>
       </c>
-      <c r="G52" t="s">
-        <v>50</v>
-      </c>
-      <c r="H52" t="s">
-        <v>98</v>
-      </c>
-      <c r="I52" t="n">
+      <c r="G53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I53" t="n">
         <v>300.0</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J53" t="n">
         <v>0.0</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K53" t="n">
         <v>300.0</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L53" t="n">
         <v>300.0</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M53" t="n">
         <v>2.02</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N53" t="n">
         <v>81801.0</v>
       </c>
-      <c r="O52" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B55" s="3" t="s">
+      <c r="O53" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>104</v>
@@ -1739,50 +1787,58 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Mai_2026.xlsx
+++ b/xlsx/carteira_mensal/Mai_2026.xlsx
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="s">
         <v>56</v>

--- a/xlsx/carteira_mensal/Mai_2026.xlsx
+++ b/xlsx/carteira_mensal/Mai_2026.xlsx
@@ -1257,7 +1257,7 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C43" t="n">
         <v>792.0</v>
@@ -1269,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G43" t="s">
         <v>56</v>

--- a/xlsx/carteira_mensal/Mai_2026.xlsx
+++ b/xlsx/carteira_mensal/Mai_2026.xlsx
@@ -204,7 +204,7 @@
     <t>joao marcelo correa cunha</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>05/05/26</t>
